--- a/results/Разметка_сравнение_RU_EN.xlsx
+++ b/results/Разметка_сравнение_RU_EN.xlsx
@@ -690,7 +690,6 @@
           <t>В душных комнатах пахло мятой .</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>177</t>
@@ -701,7 +700,6 @@
           <t>The stuffy rooms smelled of mint .</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -714,7 +712,6 @@
           <t>Красные его цветы и листья с колючками издавали в жару приторный запах .</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>178</t>
@@ -725,7 +722,6 @@
           <t>In the heat their red flowers and prickly leaves gave off a sickly sweet smell .</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -738,7 +734,6 @@
           <t>Брусок издавал тончайший запах роз .</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>182</t>
@@ -749,7 +744,6 @@
           <t>The bar gave off the faintest smell of roses .</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -762,7 +756,6 @@
           <t>В хате пахло топленым молоком .</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>184</t>
@@ -773,7 +766,6 @@
           <t>The cottage smelled of warm milk .</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -786,7 +778,6 @@
           <t>От его чешуи шел удивительный запах подводного царства .</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>186</t>
@@ -797,7 +788,6 @@
           <t>The carp ’s scales smelled of a wondrous , underwater realm .</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -810,7 +800,6 @@
           <t>От нее пахло мокрым ситцем .</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>187</t>
@@ -821,7 +810,6 @@
           <t>She smelled of damp calico .</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -834,7 +822,6 @@
           <t>Кромешная эта темнота сладковато пахла цветами .</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>188</t>
@@ -845,7 +832,6 @@
           <t>In this utter darkness I could hear the breathing of hundreds of people ; there was the slightly sweet smell of flowers .</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -858,7 +844,6 @@
           <t>Запах цветов проникал даже в дедушкин мезонин и вытеснял оттуда табачный перегар .</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>189</t>
@@ -869,7 +854,6 @@
           <t>The scent of all those flowers made its way inside to Grandfather ’s room on the mezzanine and drove out the tobacco fug .</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -882,7 +866,6 @@
           <t>Только удивительный запах выдавал ее сказочное происхождение .</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>190</t>
@@ -893,7 +876,6 @@
           <t>Mignonette was a poor girl in a darned , grey dress , but her remarkable scent gave away her fairytale lineage .</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -906,7 +888,6 @@
           <t>Когда противни с горячими « мазурками » вынимали из печки , дом наполнялся такими запахами , что даже дедушка начинал нервничать в своем мезонине .</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>192</t>
@@ -917,7 +898,6 @@
           <t>When the baking tins with the hot mazurkas came out of the oven , such delicious smells wafted through the house that even Grandfather in his mezzanine would get all worked up .</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -930,7 +910,6 @@
           <t>— У вас волосы пахнут порохом , — сказала тетя Надя .</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>193</t>
@@ -941,7 +920,6 @@
           <t>‘ Your hair reeks of gunpowder , ’ said Aunt Nadya .</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -954,7 +932,6 @@
           <t>От него действительно пахло порохом .</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>194</t>
@@ -965,7 +942,6 @@
           <t>He really did smell of gunpowder .</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -978,7 +954,6 @@
           <t>Я продирался через молодой сосняк , изодрался вконец , но какой запах , какие сухие белые гвоздики , рыжая хвоя , какая паутина !</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>195</t>
@@ -989,7 +964,6 @@
           <t>I forced my way through a young pine forest , and yes , I got all torn up , but what smells , what dry white pinks , what red pine needles , and what a spider ’s web !</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1002,7 +976,6 @@
           <t>Темнота театрального зала , запах духов и апельсиновых корок — все это казалось мне настолько заманчивым , что я мечтал спрятаться под креслом и провести всю ночь в пустом театре .</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>196</t>
@@ -1013,7 +986,6 @@
           <t>The darkness of the hall , the lingering smell of perfume and orange peel – all this enticed me so that I dreamed of hiding under my seat and spending the whole night alone in the empty theatre .</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1026,7 +998,6 @@
           <t>Мне нравились театральные коридоры с зеркалами в тусклых золотых рамах , темные вешалки , где пахло мехом от шуб , перламутровые бинокли , топот застоявшихся лошадей у театрального подъезда .</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>197</t>
@@ -1037,7 +1008,6 @@
           <t>I loved the theatre ’s long corridors with their mirrors in faded gilt frames , the dark cloakrooms that smelled of fur , the mother of pearl opera glasses , the impatient stamping of horses ’ hooves waiting before the entrance .</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1050,7 +1020,6 @@
           <t>Острые запахи ярмарочных товаров были слышны издалека .</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>198</t>
@@ -1061,7 +1030,6 @@
           <t>The strong smells of the various wares travelled far – new barrels , leather , gingerbread and calico .</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1074,7 +1042,6 @@
           <t>Пахло новыми бочками , кожей , пряниками и коленкором .</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>198</t>
@@ -1085,7 +1052,6 @@
           <t>The strong smells of the various wares travelled far – new barrels , leather , gingerbread and calico .</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1098,7 +1064,6 @@
           <t>Пароходный дым развязно влетал в окна , смешиваясь с запахом гнилого рассола и новеньких , веселых рогож .</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>202</t>
@@ -1109,7 +1074,6 @@
           <t>Smoke from the ships wafted through the open windows and mixed with the smell of old brine and fresh , new matting .</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1122,7 +1086,6 @@
           <t>— Пахнет озоном , — сказал отец .</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>203</t>
@@ -1133,7 +1096,6 @@
           <t>‘ It smells of ozone , ’ said Father .</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1146,7 +1108,6 @@
           <t>Я не знал , чем пахло вокруг , но мне казалось , что меня завалили ворохом веток , смоченных душистым дождем .</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>204</t>
@@ -1157,7 +1118,6 @@
           <t>I did not recognise the smell , but it seemed to me as if I had been covered in heaps of rain soaked twigs .</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1170,7 +1130,6 @@
           <t>Потом мы снова висели в окне , дурея от запаха цветущей гречихи .</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>205</t>
@@ -1181,7 +1140,6 @@
           <t>Then we ’d hang out of the window again and become light headed from the scent of the flowering buckwheat .</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1194,7 +1152,6 @@
           <t>От него пахло лошадиным потом и сеном .</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>206</t>
@@ -1205,7 +1162,6 @@
           <t>He smelled of horse sweat and hay .</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1218,7 +1174,6 @@
           <t>Тянуло сыростью , запахом осоки .</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>207</t>
@@ -1229,7 +1184,6 @@
           <t>The air was damp and smelled of sedge .</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1242,7 +1196,6 @@
           <t>Она тормошила меня , смеялась своим грудным смехом , и от нее пахло ванилью , — должно быть , она недавно возилась со сладким тестом .</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>209</t>
@@ -1253,7 +1206,6 @@
           <t>She snuggled me like a baby , chuckling with a deep laugh , and gave off the aroma of vanilla – she must have come straight from baking something sweet .</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1266,7 +1218,6 @@
           <t>Ярче было солнце , сильнее пахли поля , громче был гром , обильнее дожди и выше трава .</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>210</t>
@@ -1277,7 +1228,6 @@
           <t>The sun was brighter , the fields were more fragrant , the thunder was louder , the rains were heavier , the grass was taller .</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1290,7 +1240,6 @@
           <t>Кисло пахло чернилами .</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>212</t>
@@ -1301,7 +1250,6 @@
           <t>Our ink reeked of acid .</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1314,7 +1262,6 @@
           <t>Он говорил гладко и сладко , распространяя запах одеколона .</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>215</t>
@@ -1325,7 +1272,6 @@
           <t>He spoke with smooth , sugary eloquence and gave off the smell of eau de Cologne .</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1338,7 +1284,6 @@
           <t>Пахло скипидаром от молодых зеленых шишек .</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>219</t>
@@ -1349,7 +1294,6 @@
           <t>The young green pinecones smelled of turpentine .</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1362,7 +1306,6 @@
           <t>В жаркие дни на заводе до одури пахло древесной трухой .</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>220</t>
@@ -1373,7 +1316,6 @@
           <t>On hot days the smell of the mill ’s wood shavings was overpowering .</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1386,7 +1328,6 @@
           <t>Когда ракеты гасли , в парк возвращалась летняя ночь с ее отдаленным криком лягушек , блеском звезд и запахом цветущих лип .</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>221</t>
@@ -1397,7 +1338,6 @@
           <t>Once the balls went out , the summer night returned to the park , with its distant croaking of frogs , glittering stars and smell of blossoming lime trees .</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1410,7 +1350,6 @@
           <t>Пахло липовым цветом .</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>222</t>
@@ -1421,7 +1360,6 @@
           <t>I stopped by the bench and could smell the lime tree blossoms .</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1434,7 +1372,6 @@
           <t>От него пахло ягодами и дымом .</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>225</t>
@@ -1445,7 +1382,6 @@
           <t>He smelled of berries and smoke .</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1458,7 +1394,6 @@
           <t>Пахло мокрой травой .</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>226</t>
@@ -1469,7 +1404,6 @@
           <t>The smell of wet grass hung in the air .</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1482,7 +1416,6 @@
           <t>От него пахло клейстером .</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>227</t>
@@ -1493,7 +1426,6 @@
           <t>He smelled of paste .</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1506,7 +1438,6 @@
           <t>В коридоре пахло гостиничным утром — одеколоном и кофе .</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>228</t>
@@ -1517,7 +1448,6 @@
           <t>The hallway had that hotel morning smell of eau de Cologne and coffee .</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1530,7 +1460,6 @@
           <t>И кто знает , может быть , острый и режущий воздух горных вершин , забрызганных кровью демона , наполнен очень слабым , очень отдаленным запахом этого приветливого лесного цветка .</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>229</t>
@@ -1541,7 +1470,6 @@
           <t>And who knows , maybe the biting , rarefied air of the mountain heights , sprinkled with the demon ’s blood , also holds a faint hint of the scent of that welcoming woodland flower .</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1554,7 +1482,6 @@
           <t>Я чувствовал теплый и свежий запах волос .</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>233</t>
@@ -1565,7 +1492,6 @@
           <t>I caught the warm , fresh scent of her hair .</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1578,7 +1504,6 @@
           <t>Я вспоминал запах ее волос , теплоту ее свежего дыхания , встревоженные серые глаза и чуть взлетающие тонкие брови .</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>234</t>
@@ -1589,7 +1514,6 @@
           <t>I recalled the smell of her hair , the fresh warmth of her breath , the troubled look in her grey eyes and the thin arch of her eyebrows .</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1602,7 +1526,6 @@
           <t>В чебуречной на базаре жарко горели мангалы , пахло пригорелым жиром и жареной кефалью .</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>235</t>
@@ -1613,7 +1536,6 @@
           <t>The flames of the braziers glowed in the market inn , and the smell of burnt fat and roast mullet hung in the air .</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1626,7 +1548,6 @@
           <t>В лавке пахло селедочным рассолом , мылом , но все заглушал чудесный запах свежих рогож , сваленных в задней комнате .</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>236</t>
@@ -1637,7 +1558,6 @@
           <t>The shop smelled of herring brine and soap and , most of all , the heavenly aroma of fresh sacking kept in the back room .</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1650,7 +1570,6 @@
           <t>Один только взгляд , как взмах черной зарницы в этих душных ночах , что настоялись на запахе лип и были полны далеким гулом Брянских лесов — бездорожных , непроходимых , врачующих сердце от хандры и измены .</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>238</t>
@@ -1661,7 +1580,6 @@
           <t>One glance , like lightning in the sultry black night filled with the scent of the lime tree blossoms and the distant hum of the Bryansk forest , wild and impenetrable and capable of healing any heart suffering from melancholy and betrayal .</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1674,7 +1592,6 @@
           <t>Пахнуло духами , свежестью сада , запахом конфет .</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>239</t>
@@ -1685,7 +1602,6 @@
           <t>The air was filled with the smell of perfume , sweets and the freshness of the garden .</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1698,7 +1614,6 @@
           <t>В бревенчатом доме , в квартире отца , пахло угольным дымом .</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>240</t>
@@ -1709,7 +1624,6 @@
           <t>Father lived in a crude log house that smelled of coal dust .</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1722,7 +1636,6 @@
           <t>Мне нравился арсенал , его низкие здания , построенные еще при Екатерине , дворы , заросшие муравой и заваленные чугунными отливками , сирень у стен мастерских , цилиндры старых паровых машин , блестевших маслянистой медью , запах спирта в лабораториях , бородатые кузнецы и литейщики и фонтан голубоватой артезианской воды , бившей из под земли около стены арсенала .</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>241</t>
@@ -1733,7 +1646,6 @@
           <t>I liked everything about the Arsenal – the low buildings dating back to the time of Catherine the Great , the courtyards overgrown with weeds and cluttered with iron castings , the lilac bushes along the workshop walls , the shiny , oily copper cylinders of old steam engines , the smell of alcohol in the laboratories , the bearded blacksmiths , the smelters , and the fountain of bluish artesian water bubbling up from a well by the Arsenal ’s outer wall .</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1746,7 +1658,6 @@
           <t>В листьях дуба , в запахе винных бочек .</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>243</t>
@@ -1757,7 +1668,6 @@
           <t>In the oak leaves , in the smell of wine barrels .</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1770,7 +1680,6 @@
           <t>Легкий , временами почти неуловимый , как отдаленный запах , а временами твердый , как металл , французский язык звучал у этих поэтов колдовством .</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>183</t>
@@ -1781,7 +1690,6 @@
           <t>The endless stars shone in the sky , and out of the damp darkness came the smell of weeds .</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1794,7 +1702,6 @@
           <t>От Субоча пахло духами .</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>245</t>
@@ -1805,7 +1712,6 @@
           <t>He smelled of eau de Cologne .</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1818,7 +1724,6 @@
           <t>С тех пор мне казалось , что сермяги нищих пахнут не хлебом и пылью дорог , а порохом и гарью .</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>246</t>
@@ -1829,7 +1734,6 @@
           <t>From then on , the rags of the beggars smelled to me not of bread and the dust of the road , but of gunpowder and arson .</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1842,7 +1746,6 @@
           <t>Он трепал листву и нес запах воды .</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>248</t>
@@ -1853,7 +1756,6 @@
           <t>The wind picked up , shaking the trees and carrying the smell of water .</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1866,7 +1768,6 @@
           <t>Запах мокрого бурьяна проникал под навес .</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>251</t>
@@ -1877,7 +1778,6 @@
           <t>The smell of wet weeds filtered into the shed .</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1890,7 +1790,6 @@
           <t>По флигелю распространялся щиплющий горло запах .</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>253</t>
@@ -1901,7 +1800,6 @@
           <t>A harsh , burning smell filled the cottage .</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1914,7 +1812,6 @@
           <t>Большие клумбы с левкоями и табаком пахли в сумерках сильно и сладко .</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>255</t>
@@ -1925,7 +1822,6 @@
           <t>Large beds with stocks and nicotiana gave off a strong , sweet smell in the twilight .</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1938,7 +1834,6 @@
           <t>Пахло дымом ароматических свечей .</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>256</t>
@@ -1949,7 +1844,6 @@
           <t>There was the smell of scented candles .</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1962,7 +1856,6 @@
           <t>Едко пахло конским навозом .</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>257</t>
@@ -1973,7 +1866,6 @@
           <t>There was a sharp smell of horse manure .</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1986,7 +1878,6 @@
           <t>Из комнаты пахло яблочным пирогом .</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>258</t>
@@ -1997,7 +1888,6 @@
           <t>From the house came the smell of apple strudel .</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2010,7 +1900,6 @@
           <t>Медвежатина пахла сосновой смолой .</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>259</t>
@@ -2021,7 +1910,6 @@
           <t>The man travelling next to me offered me some cured bear meat ; it smelled of pine pitch .</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2034,7 +1922,6 @@
           <t>В комнате пахло палеными волосами : Галя , завиваясь на ощупь , сожгла длинную прядь .</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>261</t>
@@ -2045,7 +1932,6 @@
           <t>The room smelled of scorched hair .</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2058,7 +1944,6 @@
           <t>У нас на Лукьяновке пахло талым снегом и корой — ветер приносил этот запах из за Днепра , из потемневших к весне черниговских лесов .</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>264</t>
@@ -2069,7 +1954,6 @@
           <t>Lukyanovka smelled of melting snow .</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2082,7 +1966,6 @@
           <t>— Чем оно лучше этого удивительного запаха некошеных лугов ?</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>265</t>
@@ -2093,7 +1976,6 @@
           <t>‘ In what way is it better than the heavenly smell of these hayfields ?</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2106,7 +1988,6 @@
           <t>От мохнатого полотенца пахло соленым морем .</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>266</t>
@@ -2117,7 +1998,6 @@
           <t>My towel smelled of sea salt .</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2130,7 +2010,6 @@
           <t>Берега реки пахли теплой травой и песком .</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>267</t>
@@ -2141,7 +2020,6 @@
           <t>The riverbanks smelled of sand and warm reeds .</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2154,7 +2032,6 @@
           <t>Мне нравилась аптека — чистенькая старая изба с половиками и геранью , фаянсовыми склянками на полках и запахом трав .</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>269</t>
@@ -2165,7 +2042,6 @@
           <t>It smelled of medicinal herbs .</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2178,7 +2054,6 @@
           <t>Южное лето накапливало в городских садах столько солнечного жара , зелени и запаха цветов , что ему было жаль расставаться с этим богатством и уступать место осени .</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>271</t>
@@ -2189,7 +2064,6 @@
           <t>Our southern summer amassed so much warm sun , so much greenery and so much scent in its city parks that it was loath to say goodbye to this bounty and make way for the approaching autumn .</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2202,7 +2076,6 @@
           <t>В его темной комнате , оклеенной обоями под дубовое дерево , пахло фиксатуаром .</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>272</t>
@@ -2213,7 +2086,6 @@
           <t>His dark room , with its imitation oak wallpaper , smelled of fixative .</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2226,7 +2098,6 @@
           <t>Кончалось лето 1914 года — грозное и тревожное лето войны , и в московском воздухе уже пробивались сладковатые и прохладные запахи осени — вялых листьев и застоялых прудов .</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>274</t>
@@ -2237,7 +2108,6 @@
           <t>The summer of 1914 was drawing to a close , that terrible and threatening first summer of war , and the Moscow air already held the smell of wilting leaves and stagnant ponds , those sweet , cool aromas of autumn .</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2250,7 +2120,6 @@
           <t>От них сильно пахло хлебом .</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>275</t>
@@ -2261,7 +2130,6 @@
           <t>They smelled of bread .</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2274,7 +2142,6 @@
           <t>Удивительный запах !</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>276</t>
@@ -2285,7 +2152,6 @@
           <t>What a smell !</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2298,7 +2164,6 @@
           <t>Воспоминание о ней связано со скрежетом трамваев , выползающих на рассвете из железных ворот парка , с тяжелой кондукторской сумкой , натиравшей плечо , и с кислым запахом меди .</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>277</t>
@@ -2309,7 +2174,6 @@
           <t>My memory of the street is tied to the screech of trams as they crawled out of the depot ’s iron gates at dawn , the strap of my heavy conductor ’s satchel cutting into my shoulder and the sour smell of copper coins .</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2322,7 +2186,6 @@
           <t>Сквозняки в вагонах , липкая грязь на полах , засыпанных обрывками билетов , прелый запах мокрой одежды и слезящиеся окна , — за ними ползли вереницы темных деревянных домишек и исхлестанные дождем вывески оптовых складов .</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>278</t>
@@ -2333,7 +2196,6 @@
           <t>Draughty cars , floors covered with slippery mud and torn ticket stubs , the musty smell of wet clothing , smudgy windows , and outside , the never ending procession of small , dark wooden houses and rain lashed warehouse signs .</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2346,7 +2208,6 @@
           <t>Пахло навозом , бараниной , сеном , щепным товаром .</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>279</t>
@@ -2357,7 +2218,6 @@
           <t>The air smelled of horse dung , mutton , hay and carpenters ’ glue .</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2370,7 +2230,6 @@
           <t>Чтобы он , извините , услышал запах весеннего навозца и грачиный грай .</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>281</t>
@@ -2381,7 +2240,6 @@
           <t>I want him to smell the manure , if you ’ll excuse me , and hear the rooks .</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2394,7 +2252,6 @@
           <t>Все в нем изобличало барство — слегка припухшие веки , запах сигары , белое заграничное кашне и трость с серебряным набалдашником .</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>282</t>
@@ -2405,7 +2262,6 @@
           <t>Everything about him spoke of wealth and status : his slightly puffy eyes , the smell of fragrant cigar smoke , the white silk muffler of foreign make , the walking stick with a silver knob .</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2418,7 +2274,6 @@
           <t>Пахло горелым луком и кофе .</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>287</t>
@@ -2429,7 +2284,6 @@
           <t>The buffet smelled of coffee and burnt onions .</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2442,7 +2296,6 @@
           <t>Тоска была в глазах у мальчика — тоска по такой вот косой избе , которой у него нет , по широким лавкам вдоль стен , по треснувшему и склеенному бумагой окошку , по запаху горячего ржаного хлеба с пригоревшими к донцу угольками .</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>288</t>
@@ -2453,7 +2306,6 @@
           <t>The boy ’s eyes were filled with longing , for the things he did not have , like a simple hut with wide benches around its walls , a broken window covered over with paper , and the smell of warm rye bread with cinders baked into the crust .</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2466,7 +2318,6 @@
           <t>С тех пор я помногу живал в деревенских избах и полюбил их за тусклый блеск бревенчатых стен , запах золы и за их суровость .</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>289</t>
@@ -2477,7 +2328,6 @@
           <t>Over the years I have often spent time in peasant huts and have come to love them for the dull sheen of their timber walls , the smell of ashes in the stove and their simple austerity , similar to that of fresh water from a spring , a bast basket or the unprepossessing flowers of a potato patch .</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2490,7 +2340,6 @@
           <t>Пахло сушеной малиной .</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>294</t>
@@ -2501,7 +2350,6 @@
           <t>It smelled of dried raspberries .</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2514,7 +2362,6 @@
           <t>Может быть , оттого , что только что миновала опасность , но дождь как будто стал теплее и с полей потянуло запахом сырой травы .</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>295</t>
@@ -2525,7 +2372,6 @@
           <t>Maybe it was because the danger had just passed , but the rain seemed warmer and the fields smelled of wet grass .</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2538,7 +2384,6 @@
           <t>С равнины тянуло горьким миндальным запахом болотных цветов .</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>296</t>
@@ -2549,7 +2394,6 @@
           <t>The air had the bitter almond smell of marsh flowers .</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2562,7 +2406,6 @@
           <t>Пахло кровью , валерьянкой и горящим спиртом .</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>297</t>
@@ -2573,7 +2416,6 @@
           <t>Everything smelled of blood , essence of valerian and burning alcohol .</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2586,7 +2428,6 @@
           <t>Мимолетный этот сон был полон запаха воды и марсельского мыла .</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>298</t>
@@ -2597,7 +2438,6 @@
           <t>Fleeting dreams of the smell of water and Marseilles soap filled my head .</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2610,7 +2450,6 @@
           <t>Но стоило подняться по широкой улице в город , как тишина и запах распустившейся сирени вплотную окружали человека .</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>300</t>
@@ -2621,7 +2460,6 @@
           <t>But if you just walked a little way up the main street into town , you found yourself enveloped in silence and the smell of lilacs .</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2634,7 +2472,6 @@
           <t>Там горел яркий свет , пахло шоколадом , щебетали две сестры — кельнерши .</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>302</t>
@@ -2645,7 +2482,6 @@
           <t>It was brightly lit inside and smelled of chocolate ; the two waitresses – sisters – were standing about chattering .</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2658,7 +2494,6 @@
           <t>Его разморило от кофейного пара , запаха ванили , сладкой кондитерской теплоты и вкрадчивого полушепота белокурых сестер .</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>303</t>
@@ -2669,7 +2504,6 @@
           <t>At a far table a sapper dozed , lulled to sleep by the warmth of the café , the smell of coffee and vanilla , and the muted voices of the blonde sisters .</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2682,7 +2516,6 @@
           <t>Но в вагонах еще стояла дневная духота , особенно у меня , в операционной , где окна были наглухо закрыты и потому никогда не выветривался запах перевязок .</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>304</t>
@@ -2693,7 +2526,6 @@
           <t>The dust of defeat , with its bitter smell of charred ruins , covered everything – the soldiers ’ faces , the grain in the fields , the guns , the train .</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2706,7 +2538,6 @@
           <t>Запах бархатцев , желтевших около каждой путевой будки , проникал даже в вагоны .</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>305</t>
@@ -2717,7 +2548,6 @@
           <t>But the train held onto the hot stuffy air of the day , especially in my operating carriage , whose windows were sealed up tight ; the smell of dressing and bandages had no escape .</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2730,7 +2560,6 @@
           <t>Пахло полынью .</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>307</t>
@@ -2741,7 +2570,6 @@
           <t>There was the smell of sage .</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2754,7 +2582,6 @@
           <t>Тогда впервые этот горьковатый запах соединился в моем представлении с близостью Черного моря .</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>308</t>
@@ -2765,7 +2592,6 @@
           <t>It was then that this bitter smell became forever associated in my mind with the Black Sea .</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2778,7 +2604,6 @@
           <t>Пахло нагретым ракушечным камнем и жареной скумбрией — сестры готовили ее около дачи на очаге .</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>311</t>
@@ -2789,7 +2614,6 @@
           <t>I smelled mussels and fried mackerel – the nurses were cooking on an open fire near the house .</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2802,7 +2626,6 @@
           <t>— В общем , — сказал врач у себя в каюте , наполненной солоноватой свежестью и запахом хорошего табака , — мне нужен один санитар для перевязочной .</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>313</t>
@@ -2813,7 +2636,6 @@
           <t>‘ In short , ’ the doctor said once we had reached his cabin , which smelled of a mixture of fresh salty sea air and fine tobacco , ‘ I need another orderly for the dressing station .</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2826,7 +2648,6 @@
           <t>Запах корицы и вся прочая чепуха .</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>314</t>
@@ -2837,7 +2658,6 @@
           <t>‘ It ’s all here in your head , it is , all those magical nights along the equator , the sunsets in Bengal , the smell of cinnamon and all that other nonsense .</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2850,7 +2670,6 @@
           <t>От усов Гронского разлетался тончайший запах фиалок .</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>317</t>
@@ -2861,7 +2680,6 @@
           <t>There was the faint smell of violets on his moustache .</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2874,7 +2692,6 @@
           <t>В ней было пусто и пахло холодным дымом .</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>318</t>
@@ -2885,7 +2702,6 @@
           <t>It was empty and reeked of stale smoke .</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2898,7 +2714,6 @@
           <t>Плач , который нельзя было отличить от смеха ( а может быть , это был действительно смех изголодавшихся людей , вдохнувших запах горячей говядины ) , стоял над толпой .</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>319</t>
@@ -2909,7 +2724,6 @@
           <t>The sound of crying , indistinguishable from laughter ( and perhaps it really was laughter , the laughter of all those famished people , overjoyed by the smell of that hot beef ) , hung over the crowd .</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2922,7 +2736,6 @@
           <t>Кто же это придумал , что как раз в их жизнь , в их деревушку , где еще не успели отцвести барвинки и еще , может быть , пахнет в халупах горячим хлебом , пришла смерть , выгнала из дому в спешке , в слезах и задушила в чужих местах , в сыпучем песке , на дороге , где железные ободья колес скрипели на расстоянии ладони от их навеки уснувших лиц ?</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>321</t>
@@ -2933,7 +2746,6 @@
           <t>Whose fault was it that death had chosen them – that it had come to their little village , where the periwinkles were still in blossom and where , perhaps , the smell of warm bread still lingered in the peasant huts , to drive them from their homes , hurrying and in tears , and to finish them off in a strange land , in thick sand , on a highway , where the metal rimmed wheels of carts creaked by just inches from their eternally resting faces ?</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2946,7 +2758,6 @@
           <t>Пахло одеколоном .</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>322</t>
@@ -2957,7 +2768,6 @@
           <t>There was the faint smell of eau de Cologne .</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2970,7 +2780,6 @@
           <t>Снова запах лошадиного едкого пота , крики : « Но , заразы ! » — скрип колес , твердое седло , пески и пески .</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>323</t>
@@ -2981,7 +2790,6 @@
           <t>Again the stench of horse sweat , the shouting , the creaking wheels , the hard saddle , and then the sand , ever more sand .</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2994,7 +2802,6 @@
           <t>Пахло пылью , поднятой копытами лошадей , и болотной водой .</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>324</t>
@@ -3005,7 +2812,6 @@
           <t>Dust from the horses and the wet smell of the bogs hung in the air .</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3018,7 +2824,6 @@
           <t>От них воняло псиной .</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>325</t>
@@ -3029,7 +2834,6 @@
           <t>We could not dry out and before long we began to smell like wet dogs in our greatcoats .</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3042,7 +2846,6 @@
           <t>Но все же сильно пахло чадом , как от паленых перьев .</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>326</t>
@@ -3053,7 +2856,6 @@
           <t>Not a wisp of smoke rose from the hovels , but for some reason the air smelled of scorched feathers .</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3066,7 +2868,6 @@
           <t>В лицо хлынула теплая вонь .</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>328</t>
@@ -3077,7 +2878,6 @@
           <t>A warm stench hit us in the face .</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3090,7 +2890,6 @@
           <t>Голубые их мундиры распространяли запах духов .</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>336</t>
@@ -3101,7 +2900,6 @@
           <t>Their light blue uniforms smelled of eau de Cologne .</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3114,7 +2912,6 @@
           <t>Иногда офицеры ссорились , и тогда в низенькой столовой у дяди Коли начинало пахнуть порохом , и казалось , вот вот сшибутся шпаги .</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>338</t>
@@ -3125,7 +2922,6 @@
           <t>Sometimes the officers quarrelled , and you could almost smell gunpowder in the air of Uncle Kolya ’s small dining room and imagine the men reaching for their swords .</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3138,7 +2934,6 @@
           <t>Пахло кислым фиксажем .</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>341</t>
@@ -3149,7 +2944,6 @@
           <t>The room had the acidic smell of fixing solution .</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3162,7 +2956,6 @@
           <t>Оно заполняло комнаты своим шумом , ветром и запахами .</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>343</t>
@@ -3173,7 +2966,6 @@
           <t>It filled the rooms with its sound , its breeze , its scent .</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3186,7 +2978,6 @@
           <t>В открытые окна вагона проникал запах водорослей .</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>345</t>
@@ -3197,7 +2988,6 @@
           <t>The smell of seaweed drifted in through the open windows of the carriage .</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3210,7 +3000,6 @@
           <t>Неистребимый запах дешевой пудры , кухонного чада и лекарств стоял повсюду .</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>346</t>
@@ -3221,7 +3010,6 @@
           <t>The entire hotel reeked of cheap face powder , strong medicines and burnt fat from the kitchen .</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3234,7 +3022,6 @@
           <t>Чем дальше я читал эту записную книжку , тем яснее проступали в памяти позабытые краски и запахи , какие то знакомые места .</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>348</t>
@@ -3245,7 +3032,6 @@
           <t>As I read along , forgotten colours and smells and details of the place came back to me , but I could not place them .</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3258,7 +3044,6 @@
           <t>Нужно нагнуться к ней , и вы услышите запах , от которого у вас забьется сердце , — запах океана и полыни , тот запах , что освежает голову и напоминает о плаваниях , целительных для сердца и плодотворных для ума .</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>349</t>
@@ -3269,7 +3054,6 @@
           <t>If you bend over a gun , your heart beats faster – the water smells of the ocean and worm wood , it ’s a smell that clears your head and reminds you of long sea voyages , the kind that heal your soul and quicken the mind .</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3282,7 +3066,6 @@
           <t>Но , в общем , выбирайте сами , к какой книге вас больше влечет эта белая от старости палуба и запах железных бортов , заросших по ватерлинии бахромой водорослей .</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>350</t>
@@ -3293,7 +3076,6 @@
           <t>Or let the old sun bleached deck and the smell of the seaweed clinging to the boat ’s iron sides along the waterline suggest something else .</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3306,7 +3088,6 @@
           <t>Ее синие глаза никогда не улыбались , а от длинных черных кос шел запах лаванды .</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>351</t>
@@ -3317,7 +3098,6 @@
           <t>Her dark blue eyes never smiled , and her long black plaits smelled of lavender .</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3330,7 +3110,6 @@
           <t>Снизу из ресторана пахло кислыми щами и самоварным дымом .</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>353</t>
@@ -3341,7 +3120,6 @@
           <t>The sour smell of cabbage soup and samovar smoke wafted up from the restaurant .</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3354,7 +3132,6 @@
           <t>Пришла первая февральская оттепель с туманами и капелью , порывистым ветром и запахом дыма .</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>356</t>
@@ -3365,7 +3142,6 @@
           <t>The first February thaw had arrived , bringing with it a wet fog , blustery winds and the smell of smoke .</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3378,7 +3154,6 @@
           <t>Этот запах , напоминавший затхлый воздух зажитых и старомодных квартир , разоблачал его .</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>359</t>
@@ -3389,7 +3164,6 @@
           <t>That smell , which brought to mind the fusty air of old fashioned apartments , gave him away .</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3402,7 +3176,6 @@
           <t>Я был почему то уверен , что лекарственные запахи несовместимы с высоким званием трибуна .</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>360</t>
@@ -3413,7 +3186,6 @@
           <t>For some reason I was convinced that medicinal smells like this were incompatible with the high calling of a champion of the people .</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3426,7 +3198,6 @@
           <t>Воздух был пропитан керосиновым запахом типографской краски и ржаного хлеба .</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>362</t>
@@ -3437,7 +3208,6 @@
           <t>The air smelled of printers ’ ink and rye bread .</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3450,7 +3220,6 @@
           <t>Этот последний деревенский запах принесла с собой армия .</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>363</t>
@@ -3461,7 +3230,6 @@
           <t>The army had brought the village smell of bread with them .</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3474,7 +3242,6 @@
           <t>Поскрипывали колеса , от старой сбруи пахло дегтем .</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>365</t>
@@ -3485,7 +3252,6 @@
           <t>The wheels creaked , the old harness smelled of tar .</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3498,7 +3264,6 @@
           <t>Горьковато пахло горелыми можжевеловыми ягодами , — ими монахи курили вместо ладана .</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>366</t>
@@ -3509,7 +3274,6 @@
           <t>There was the slightly bitter smell of burned juniper berries , which the monks used instead of incense .</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3522,7 +3286,6 @@
           <t>Поздняя ночь пахла дымом пожарищ .</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>367</t>
@@ -3533,7 +3296,6 @@
           <t>The late night air smelled of smoke from the burning houses .</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3546,7 +3308,6 @@
           <t>На московских улицах все так же пахло типографской краской , а на стенах висели сырые обрывки газет и плакатов .</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>368</t>
@@ -3557,7 +3318,6 @@
           <t>The Moscow streets still smelled of printers ’ ink , and tattered scraps of old newspapers and posters clung to the walls .</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3570,7 +3330,6 @@
           <t>Они привозили с собой запах мороза , яблок и зипунов .</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>369</t>
@@ -3581,7 +3340,6 @@
           <t>They brought with them the aroma of apples , homespun and frost .</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3594,7 +3352,6 @@
           <t>Запах яблок был крепкий , от зипунов исходило ощущение прочности и тепла , и почему то от этого становилось спокойнее на душе .</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>370</t>
@@ -3605,7 +3362,6 @@
           <t>For some reason I found the apples ’ strong smell and the homespun ’s suggestion of warmth and durability comforting .</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3618,7 +3374,6 @@
           <t>Старик тщательно рассматривал эти письма и даже нюхал их , будто они могли пахнуть тропическими плодами .</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>371</t>
@@ -3629,7 +3384,6 @@
           <t>He even sniffed the envelopes , thinking he might pick up the sweet scent of tropical fruit , but they only smelled of leather and sealing wax .</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3642,7 +3396,6 @@
           <t>Но письма пахли сургучом и кожей .</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>371</t>
@@ -3653,7 +3406,6 @@
           <t>He even sniffed the envelopes , thinking he might pick up the sweet scent of tropical fruit , but they only smelled of leather and sealing wax .</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3666,7 +3418,6 @@
           <t>Тотчас запах паленой шерсти распространялся вокруг .</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>372</t>
@@ -3677,7 +3428,6 @@
           <t>Immediately the stench of scorched wool filled the air .</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3690,7 +3440,6 @@
           <t>Я услышал запах перепрелой листвы , похожий на слабое дыхание вина , запах растительной горечи и оттаявших прошлогодних цветов .</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>373</t>
@@ -3701,7 +3450,6 @@
           <t>I caught the smell of rotting leaves , like the faint bouquet of wine , of bitter vegetable matter and last year ’s thawed out flowers , which seemed to be seeping out from deep down inside the damp , shelterless and long untended soil .</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3714,7 +3462,6 @@
           <t>Он начал этот рассказ не с описания дома , а с целого исследования о запахе деревянных турецких домов .</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>375</t>
@@ -3725,7 +3472,6 @@
           <t>He never began the story with a description of the house , but with an elaborate discourse on the distinctive smell of Turkish wooden houses .</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3738,7 +3484,6 @@
           <t>Дома эти , как утверждал Розовский , пахли теплой древесной трухой и медом .</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>376</t>
@@ -3749,7 +3494,6 @@
           <t>According to Rozovsky , they all smelled of the warm dust of rotting wood and of honey , particularly on hot , still afternoons when if you so much as touched the verandah railing it would singe your hand .</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3762,7 +3506,6 @@
           <t>В запахе древесной трухи всегда чувствуется привкус сухих роз .</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>377</t>
@@ -3773,7 +3516,6 @@
           <t>The smell of dust was always mixed with a faint hint of dry roses .</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3786,7 +3528,6 @@
           <t>А медом дома эти пахли оттого , что вокруг в масличных садах с кустами дичающих роз водилось много пчел и они строили соты на чердаках домов , и потому то дома так сладко пахли медом .</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>378</t>
@@ -3797,7 +3538,6 @@
           <t>The smell of honey came from the surrounding olive gardens filled with wild roses .</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3810,7 +3550,6 @@
           <t>Впервые этот приторный запах высохших роз и меда Розовский услышал в Константинополе , когда ему показали осыпанный грубо отшлифованными драгоценными камнями ларец , где хранилось зеленое знамя Пророка .</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>380</t>
@@ -3821,7 +3560,6 @@
           <t>Rozovsky first encountered the thick smell of dried roses and honey in Constantinople , when he was shown the gem encrusted casket holding the green banner of the Prophet .</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3834,7 +3572,6 @@
           <t>Пахло кислятиной , мокрыми шинелями и карболкой .</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>382</t>
@@ -3845,7 +3582,6 @@
           <t>There was a sour smell of wet greatcoats and carbolic acid .</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3858,7 +3594,6 @@
           <t>Мне нравился сумрак зала , его гулкая пустота , две три лампочки в хрустальных чашечках , одиноко горевшие в разных углах , даже тот гостиничный запах пыльных ковров , что никогда не выветривался из « Метрополя » .</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>383</t>
@@ -3869,7 +3604,6 @@
           <t>I enjoyed the hall ’s dim light , its echoing emptiness , the two or three bulbs glowing in the crystal wall sconces deep in the corners and even that hotel smell of dusty carpets that no amount of airing could dispel .</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3882,7 +3616,6 @@
           <t>Иногда ветер наполнял улицу запахом гниющей воды и помидоровых листьев .</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>384</t>
@@ -3893,7 +3626,6 @@
           <t>Now and then the wind filled the street with the smell of stagnant water and tomato plants .</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3906,7 +3638,6 @@
           <t>От нее пахло аптекой .</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>385</t>
@@ -3917,7 +3648,6 @@
           <t>It all smelled like a chemist ’s shop .</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3930,7 +3660,6 @@
           <t>Во влажных его зарослях освежающе пахло укропом и мятой .</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>386</t>
@@ -3941,7 +3670,6 @@
           <t>Its green freshness was full of the rich smell of dill and mint .</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3954,7 +3682,6 @@
           <t>Их сильный запах казался занесенным сюда из отдаленной южной весны .</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>387</t>
@@ -3965,7 +3692,6 @@
           <t>Their strong smell seemed as though it had somehow been transported here from some springtime in a far off southern clime .</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3978,7 +3704,6 @@
           <t>У каждого хранится на душе , как тонкий запах лип из Ноевского сада , память о проблеске счастья , заваленном потом житейским мусором .</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>388</t>
@@ -3989,7 +3714,6 @@
           <t>Everyone , I am sure , treasures in their soul some memory , as delicate as the scent of the lime trees in Noevsky Gardens , of a glimmer of happiness long buried under the squalor of everyday life .</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4002,7 +3726,6 @@
           <t>Все , связанное с железной дорогой , до сих пор овеяно для меня поэзией путешествий , даже запах каменноугольного дыма из паровозных топок .</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>389</t>
@@ -4013,7 +3736,6 @@
           <t>Whenever our family passed the summer holidays near a railway station , I spent hours there meeting and seeing off every single train together with the station guard in his red cap . Even now , every last thing about railways still has for me the poetry of travel about it , all the way down to the smell of the coal smoke from the engine .</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4026,7 +3748,6 @@
           <t>Запах кофе из комнаты девицы Кностер почему то вызывал представление о сочельнике .</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>391</t>
@@ -4037,7 +3758,6 @@
           <t>For some reason the smell of coffee coming from Frau Knoster ’s room brought back memories of Christmas Eve .</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4050,7 +3770,6 @@
           <t>От пана Ктуренды исходил сложный запах усатина , табачного перегара и самогона .</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>392</t>
@@ -4061,7 +3780,6 @@
           <t>Pan Kturenda gave off a complex aroma of hair dye , stale tobacco and hooch , which he distilled himself in his own dimly lit room .</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4074,7 +3792,6 @@
           <t>Нечто успокоительное чувствовалось в запахе скудной еды , еще сохранившемся в кухне .</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>397</t>
@@ -4085,7 +3802,6 @@
           <t>There was something comforting about the smell of old food that clung to the kitchens .</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4098,7 +3814,6 @@
           <t>Все перепуталось , — Варя Панина и гранаты , запах йодоформа и украинская певучая « мова » , красные ленты на папахах и симфонические концерты , мечты богунцев о тихих прудах среди веселых левад и истерические визгливые облавы на базарах .</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>398</t>
@@ -4109,7 +3824,6 @@
           <t>Everything was all jumbled together – Varya Panina&gt;1 and hand grenades , the smell of iodoform and the soft sing song of Ukrainian speech , the red cockades on the Cossack hats and symphony concerts , soldiers ’ dreams of still ponds amid peaceful meadows and the hysterical cries of illegal traders being rounded up in the bazaars .</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4122,7 +3836,6 @@
           <t>Они принесли с собой запах пороха , красные знамена , простреленные в боях , удалые песни и беззаветную свою преданность революции .</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>399</t>
@@ -4133,7 +3846,6 @@
           <t>They had brought with them the smell of battle , bullet ridden red banners , dashing songs and a selfless devotion to the revolution .</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4146,7 +3858,6 @@
           <t>Их запах проник в запущенные за зиму , закупоренные дома и заставил горожан распахнуть окна и балконы .</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>400</t>
@@ -4157,7 +3868,6 @@
           <t>At long last , the lime trees blossomed in the parks , and their scent filtered into the houses sealed up tight over the winter and forced the city dwellers to throw open their windows and balcony doors .</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4170,7 +3880,6 @@
           <t>Запах теплой и вялой летней листвы проникал в разбитые окна .</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>401</t>
@@ -4181,7 +3890,6 @@
           <t>The warm , drowsy smell of summer leaves drifted through the broken windows .</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4194,7 +3902,6 @@
           <t>Внутри форта так густо пахло казармой , что одежда мгновенно и навсегда пропитывалась этим запахом .</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>402</t>
@@ -4205,7 +3912,6 @@
           <t>The barrack stench was so strong that it immediately settled into my clothes and never left .</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4218,7 +3924,6 @@
           <t>Пахло пыльной травой , и было слышно , как на колокольне в Печерской лавре пробило четыре никому не нужных часа .</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>403</t>
@@ -4229,7 +3934,6 @@
           <t>There was the smell of dusty grass , and the bells of the Pechersk Monastery struck the useless hour of four o ’clock .</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4242,7 +3946,6 @@
           <t>Откуда то пахло цветущей маттиолой .</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>404</t>
@@ -4253,7 +3956,6 @@
           <t>The air was filled with the smell of flowering stocks .</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4266,7 +3968,6 @@
           <t>Из палисадника пахло травой .</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>405</t>
@@ -4277,7 +3978,6 @@
           <t>The smell of grass came from the front gardens .</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4290,7 +3990,6 @@
           <t>В темноватой квартире у Амалии пахло свежеразмолотым кофе .</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>407</t>
@@ -4301,7 +4000,6 @@
           <t>Amalia ’s dark flat smelled of fresh coffee .</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4314,7 +4012,6 @@
           <t>Как всегда , от запаха кофе казалось , что в квартире было уютнее , хотя висевший на стене « подарок моря » — испорченный термометр , украшенный ракушками , — и зиму и лето показывал одно и то же : три градуса холода .</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>408</t>
@@ -4325,7 +4022,6 @@
           <t>As always , the smell of coffee made the flat seem cosier , despite the ‘ Gift of the Sea ’ – a broken wall mounted thermometer decorated with cockle shells that read three degrees below zero both winter and summer .</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4338,7 +4034,6 @@
           <t>Цветы были хороши , но пахли краской , клеем и очень скоро пылились .</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>409</t>
@@ -4349,7 +4044,6 @@
           <t>Her flowers were pretty , but they smelled of paint and glue and very quickly gathered dust .</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4362,7 +4056,6 @@
           <t>И цветы белых лилий склонились к их легким подолам , распространяя аромат целомудрия .</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>411</t>
@@ -4373,7 +4066,6 @@
           <t>A great many women had travelled the same path from sin to sanctity , and as proof faint gold haloes had been lit over their heads in the paintings of the Great Masters of the Renaissance , and white lilies brushed their hems , spreading the scent of chastity .</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4386,7 +4078,6 @@
           <t>Из за заборов пахло бархатцами .</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>412</t>
@@ -4397,7 +4088,6 @@
           <t>The smell of marigolds drifted from behind the fences .</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4410,7 +4100,6 @@
           <t>Когда я вспоминал , например , гостиницы , я вызывал у себя в памяти все мелочи , связанные с ними , — цвет затертых дорожек в коридорах , рисунок обоев , гостиничные запахи и олеографии , лица гостиничных девушек и их манеру говорить , затасканную гнутую мебель , — все , вплоть до чернильницы из похожего по цвету на мокрый сахар уральского камня , где никогда не было чернил и лежали совершенно высохшие мушиные трупы .</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>413</t>
@@ -4421,7 +4110,6 @@
           <t>I would try to retrieve from my memory every last detail – the colour of the faded runners in the corridors , the wall paper designs , the various smells , the prints on the walls , the faces of the maids , the way they talked , the worn bentwood furniture – everything right down to the inkwells made of stone from the Urals the colour of damp sugar which were always filled with a few dead flies but never any ink .</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4434,7 +4122,6 @@
           <t>Каштаны трещали , лопались и распространяли запах чуть пригорелой коры , но с душистым и сладким привкусом .</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>414</t>
@@ -4445,7 +4132,6 @@
           <t>The chestnuts crackled , burst and gave off an aroma of burnt bark , although sweeter and more fragrant .</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4458,7 +4144,6 @@
           <t>Я полюбил запах тумана , — слабый запах каменноугольного дыма и пара .</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>416</t>
@@ -4469,7 +4154,6 @@
           <t>I loved the smell of fog as well , which carried with it a scent of coal smoke and steam .</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4482,7 +4166,6 @@
           <t>То был запах вокзалов , пристаней , палуб — всего , что связано со странствиями , со сменой обширных сухопутных и морских пространств , с шествием в светоносной фиолетовой синеве архипелага далеких розовеющих островов , откуда ветер доносит слабый запах лимона , с сырым ветром и беспокойными огнями плавучих маяков Ла Манша , с плавным ходом поезда сквозь наши дремлющие лесные края , со всем , что берет в пожизненный плен наше слабое человеческое сердце .</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>417</t>
@@ -4493,7 +4176,6 @@
           <t>It was the smell of railway stations , of docks and ship decks – everything that spoke of travel , of long journeys over land and sea , of voyages through violet blue light to distant pink islands bathed in the sweet aroma of lemons , of the raw wind and warning lights in the English Channel , of the rhythmic clatter of a train rolling through our slumbering Russian forests , of everything that captivates our frail human hearts .</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4506,7 +4188,6 @@
           <t>Они кисло пахли порохом .</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>419</t>
@@ -4517,7 +4198,6 @@
           <t>The cartridges had an acrid smell of gunpowder .</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4530,7 +4210,6 @@
           <t>Я это знал по запаху мокрой гальки и по едва внятному трепету одинокого платанового листа .</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>421</t>
@@ -4541,7 +4220,6 @@
           <t>I could tell by the smell of the wet shingle and the subtle trembling of the last leaf on the plane tree .</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4554,7 +4232,6 @@
           <t>Даже море пахнет ржавым железом .</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>422</t>
@@ -4565,7 +4242,6 @@
           <t>Even the sea smells of rusty iron . ’</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8220,9 +7896,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L164"/>
+  <dimension ref="A1:P164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -8284,6 +7961,12 @@
           <t>sentiment_EN</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v/>
+      </c>
+      <c r="P2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8311,6 +7994,12 @@
           <t>The stuffy rooms smelled of mint .</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8333,6 +8022,12 @@
           <t>In the heat their red flowers and prickly leaves gave off a sickly sweet smell .</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8360,6 +8055,12 @@
           <t>The bar gave off the faintest smell of roses .</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8392,6 +8093,12 @@
           <t>The cottage smelled of warm milk .</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8414,6 +8121,12 @@
           <t>The carp ’s scales smelled of a wondrous , underwater realm .</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8446,6 +8159,12 @@
           <t>She smelled of damp calico .</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8468,6 +8187,12 @@
           <t>In this utter darkness I could hear the breathing of hundreds of people ; there was the slightly sweet smell of flowers .</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8490,6 +8215,12 @@
           <t>The scent of all those flowers made its way inside to Grandfather ’s room on the mezzanine and drove out the tobacco fug .</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8512,6 +8243,12 @@
           <t>Mignonette was a poor girl in a darned , grey dress , but her remarkable scent gave away her fairytale lineage .</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v/>
+      </c>
+      <c r="P11" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8534,6 +8271,12 @@
           <t>When the baking tins with the hot mazurkas came out of the oven , such delicious smells wafted through the house that even Grandfather in his mezzanine would get all worked up .</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v/>
+      </c>
+      <c r="P12" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8561,6 +8304,12 @@
           <t>‘ Your hair reeks of gunpowder , ’ said Aunt Nadya .</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v/>
+      </c>
+      <c r="P13" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8583,6 +8332,12 @@
           <t>He really did smell of gunpowder .</t>
         </is>
       </c>
+      <c r="O14" t="n">
+        <v/>
+      </c>
+      <c r="P14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8605,6 +8360,12 @@
           <t>I forced my way through a young pine forest , and yes , I got all torn up , but what smells , what dry white pinks , what red pine needles , and what a spider ’s web !</t>
         </is>
       </c>
+      <c r="O15" t="n">
+        <v/>
+      </c>
+      <c r="P15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8627,6 +8388,12 @@
           <t>The darkness of the hall , the lingering smell of perfume and orange peel – all this enticed me so that I dreamed of hiding under my seat and spending the whole night alone in the empty theatre .</t>
         </is>
       </c>
+      <c r="O16" t="n">
+        <v/>
+      </c>
+      <c r="P16" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8649,6 +8416,12 @@
           <t>I loved the theatre ’s long corridors with their mirrors in faded gilt frames , the dark cloakrooms that smelled of fur , the mother of pearl opera glasses , the impatient stamping of horses ’ hooves waiting before the entrance .</t>
         </is>
       </c>
+      <c r="O17" t="n">
+        <v/>
+      </c>
+      <c r="P17" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8671,6 +8444,12 @@
           <t>The strong smells of the various wares travelled far – new barrels , leather , gingerbread and calico .</t>
         </is>
       </c>
+      <c r="O18" t="n">
+        <v/>
+      </c>
+      <c r="P18" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8693,6 +8472,12 @@
           <t>The strong smells of the various wares travelled far – new barrels , leather , gingerbread and calico .</t>
         </is>
       </c>
+      <c r="O19" t="n">
+        <v/>
+      </c>
+      <c r="P19" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8715,6 +8500,12 @@
           <t>Smoke from the ships wafted through the open windows and mixed with the smell of old brine and fresh , new matting .</t>
         </is>
       </c>
+      <c r="O20" t="n">
+        <v/>
+      </c>
+      <c r="P20" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8737,6 +8528,12 @@
           <t>‘ It smells of ozone , ’ said Father .</t>
         </is>
       </c>
+      <c r="O21" t="n">
+        <v/>
+      </c>
+      <c r="P21" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8759,6 +8556,12 @@
           <t>I did not recognise the smell , but it seemed to me as if I had been covered in heaps of rain soaked twigs .</t>
         </is>
       </c>
+      <c r="O22" t="n">
+        <v/>
+      </c>
+      <c r="P22" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8781,6 +8584,12 @@
           <t>Then we ’d hang out of the window again and become light headed from the scent of the flowering buckwheat .</t>
         </is>
       </c>
+      <c r="O23" t="n">
+        <v/>
+      </c>
+      <c r="P23" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8803,6 +8612,12 @@
           <t>He smelled of horse sweat and hay .</t>
         </is>
       </c>
+      <c r="O24" t="n">
+        <v/>
+      </c>
+      <c r="P24" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8825,6 +8640,12 @@
           <t>The air was damp and smelled of sedge .</t>
         </is>
       </c>
+      <c r="O25" t="n">
+        <v/>
+      </c>
+      <c r="P25" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8847,6 +8668,12 @@
           <t>She snuggled me like a baby , chuckling with a deep laugh , and gave off the aroma of vanilla – she must have come straight from baking something sweet .</t>
         </is>
       </c>
+      <c r="O26" t="n">
+        <v/>
+      </c>
+      <c r="P26" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8869,6 +8696,12 @@
           <t>The sun was brighter , the fields were more fragrant , the thunder was louder , the rains were heavier , the grass was taller .</t>
         </is>
       </c>
+      <c r="O27" t="n">
+        <v/>
+      </c>
+      <c r="P27" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8896,6 +8729,12 @@
           <t>Our ink reeked of acid .</t>
         </is>
       </c>
+      <c r="O28" t="n">
+        <v/>
+      </c>
+      <c r="P28" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8918,6 +8757,12 @@
           <t>He spoke with smooth , sugary eloquence and gave off the smell of eau de Cologne .</t>
         </is>
       </c>
+      <c r="O29" t="n">
+        <v/>
+      </c>
+      <c r="P29" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8940,6 +8785,12 @@
           <t>The young green pinecones smelled of turpentine .</t>
         </is>
       </c>
+      <c r="O30" t="n">
+        <v/>
+      </c>
+      <c r="P30" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8962,6 +8813,12 @@
           <t>On hot days the smell of the mill ’s wood shavings was overpowering .</t>
         </is>
       </c>
+      <c r="O31" t="n">
+        <v/>
+      </c>
+      <c r="P31" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8984,6 +8841,12 @@
           <t>Once the balls went out , the summer night returned to the park , with its distant croaking of frogs , glittering stars and smell of blossoming lime trees .</t>
         </is>
       </c>
+      <c r="O32" t="n">
+        <v/>
+      </c>
+      <c r="P32" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9006,6 +8869,12 @@
           <t>I stopped by the bench and could smell the lime tree blossoms .</t>
         </is>
       </c>
+      <c r="O33" t="n">
+        <v/>
+      </c>
+      <c r="P33" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9028,6 +8897,12 @@
           <t>He smelled of berries and smoke .</t>
         </is>
       </c>
+      <c r="O34" t="n">
+        <v/>
+      </c>
+      <c r="P34" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9055,6 +8930,12 @@
           <t>The smell of wet grass hung in the air .</t>
         </is>
       </c>
+      <c r="O35" t="n">
+        <v/>
+      </c>
+      <c r="P35" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9077,6 +8958,12 @@
           <t>He smelled of paste .</t>
         </is>
       </c>
+      <c r="O36" t="n">
+        <v/>
+      </c>
+      <c r="P36" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9099,6 +8986,12 @@
           <t>The hallway had that hotel morning smell of eau de Cologne and coffee .</t>
         </is>
       </c>
+      <c r="O37" t="n">
+        <v/>
+      </c>
+      <c r="P37" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9121,6 +9014,12 @@
           <t>And who knows , maybe the biting , rarefied air of the mountain heights , sprinkled with the demon ’s blood , also holds a faint hint of the scent of that welcoming woodland flower .</t>
         </is>
       </c>
+      <c r="O38" t="n">
+        <v/>
+      </c>
+      <c r="P38" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9148,6 +9047,12 @@
           <t>I caught the warm , fresh scent of her hair .</t>
         </is>
       </c>
+      <c r="O39" t="n">
+        <v/>
+      </c>
+      <c r="P39" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9175,6 +9080,12 @@
           <t>I recalled the smell of her hair , the fresh warmth of her breath , the troubled look in her grey eyes and the thin arch of her eyebrows .</t>
         </is>
       </c>
+      <c r="O40" t="n">
+        <v/>
+      </c>
+      <c r="P40" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9197,6 +9108,12 @@
           <t>The flames of the braziers glowed in the market inn , and the smell of burnt fat and roast mullet hung in the air .</t>
         </is>
       </c>
+      <c r="O41" t="n">
+        <v/>
+      </c>
+      <c r="P41" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9224,6 +9141,12 @@
           <t>The shop smelled of herring brine and soap and , most of all , the heavenly aroma of fresh sacking kept in the back room .</t>
         </is>
       </c>
+      <c r="O42" t="n">
+        <v/>
+      </c>
+      <c r="P42" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9246,6 +9169,12 @@
           <t>One glance , like lightning in the sultry black night filled with the scent of the lime tree blossoms and the distant hum of the Bryansk forest , wild and impenetrable and capable of healing any heart suffering from melancholy and betrayal .</t>
         </is>
       </c>
+      <c r="O43" t="n">
+        <v/>
+      </c>
+      <c r="P43" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9273,6 +9202,12 @@
           <t>The air was filled with the smell of perfume , sweets and the freshness of the garden .</t>
         </is>
       </c>
+      <c r="O44" t="n">
+        <v/>
+      </c>
+      <c r="P44" t="n">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9295,6 +9230,12 @@
           <t>Father lived in a crude log house that smelled of coal dust .</t>
         </is>
       </c>
+      <c r="O45" t="n">
+        <v/>
+      </c>
+      <c r="P45" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9317,6 +9258,12 @@
           <t>I liked everything about the Arsenal – the low buildings dating back to the time of Catherine the Great , the courtyards overgrown with weeds and cluttered with iron castings , the lilac bushes along the workshop walls , the shiny , oily copper cylinders of old steam engines , the smell of alcohol in the laboratories , the bearded blacksmiths , the smelters , and the fountain of bluish artesian water bubbling up from a well by the Arsenal ’s outer wall .</t>
         </is>
       </c>
+      <c r="O46" t="n">
+        <v/>
+      </c>
+      <c r="P46" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9339,6 +9286,12 @@
           <t>In the oak leaves , in the smell of wine barrels .</t>
         </is>
       </c>
+      <c r="O47" t="n">
+        <v/>
+      </c>
+      <c r="P47" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9361,6 +9314,12 @@
           <t>The endless stars shone in the sky , and out of the damp darkness came the smell of weeds .</t>
         </is>
       </c>
+      <c r="O48" t="n">
+        <v/>
+      </c>
+      <c r="P48" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9388,6 +9347,12 @@
           <t>He smelled of eau de Cologne .</t>
         </is>
       </c>
+      <c r="O49" t="n">
+        <v/>
+      </c>
+      <c r="P49" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9410,6 +9375,12 @@
           <t>From then on , the rags of the beggars smelled to me not of bread and the dust of the road , but of gunpowder and arson .</t>
         </is>
       </c>
+      <c r="O50" t="n">
+        <v/>
+      </c>
+      <c r="P50" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9437,6 +9408,12 @@
           <t>The wind picked up , shaking the trees and carrying the smell of water .</t>
         </is>
       </c>
+      <c r="O51" t="n">
+        <v/>
+      </c>
+      <c r="P51" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9464,6 +9441,12 @@
           <t>The smell of wet weeds filtered into the shed .</t>
         </is>
       </c>
+      <c r="O52" t="n">
+        <v/>
+      </c>
+      <c r="P52" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9486,6 +9469,12 @@
           <t>A harsh , burning smell filled the cottage .</t>
         </is>
       </c>
+      <c r="O53" t="n">
+        <v/>
+      </c>
+      <c r="P53" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9508,6 +9497,12 @@
           <t>Large beds with stocks and nicotiana gave off a strong , sweet smell in the twilight .</t>
         </is>
       </c>
+      <c r="O54" t="n">
+        <v/>
+      </c>
+      <c r="P54" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9535,6 +9530,12 @@
           <t>There was the smell of scented candles .</t>
         </is>
       </c>
+      <c r="O55" t="n">
+        <v/>
+      </c>
+      <c r="P55" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9557,6 +9558,12 @@
           <t>There was a sharp smell of horse manure .</t>
         </is>
       </c>
+      <c r="O56" t="n">
+        <v/>
+      </c>
+      <c r="P56" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9584,6 +9591,12 @@
           <t>From the house came the smell of apple strudel .</t>
         </is>
       </c>
+      <c r="O57" t="n">
+        <v/>
+      </c>
+      <c r="P57" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9606,6 +9619,12 @@
           <t>The man travelling next to me offered me some cured bear meat ; it smelled of pine pitch .</t>
         </is>
       </c>
+      <c r="O58" t="n">
+        <v/>
+      </c>
+      <c r="P58" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9633,6 +9652,12 @@
           <t>The room smelled of scorched hair .</t>
         </is>
       </c>
+      <c r="O59" t="n">
+        <v/>
+      </c>
+      <c r="P59" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9655,6 +9680,12 @@
           <t>Lukyanovka smelled of melting snow .</t>
         </is>
       </c>
+      <c r="O60" t="n">
+        <v/>
+      </c>
+      <c r="P60" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9677,6 +9708,12 @@
           <t>‘ In what way is it better than the heavenly smell of these hayfields ?</t>
         </is>
       </c>
+      <c r="O61" t="n">
+        <v/>
+      </c>
+      <c r="P61" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9699,6 +9736,12 @@
           <t>My towel smelled of sea salt .</t>
         </is>
       </c>
+      <c r="O62" t="n">
+        <v/>
+      </c>
+      <c r="P62" t="n">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9726,6 +9769,12 @@
           <t>The riverbanks smelled of sand and warm reeds .</t>
         </is>
       </c>
+      <c r="O63" t="n">
+        <v/>
+      </c>
+      <c r="P63" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9753,6 +9802,12 @@
           <t>It smelled of medicinal herbs .</t>
         </is>
       </c>
+      <c r="O64" t="n">
+        <v/>
+      </c>
+      <c r="P64" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9775,6 +9830,12 @@
           <t>Our southern summer amassed so much warm sun , so much greenery and so much scent in its city parks that it was loath to say goodbye to this bounty and make way for the approaching autumn .</t>
         </is>
       </c>
+      <c r="O65" t="n">
+        <v/>
+      </c>
+      <c r="P65" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9797,6 +9858,12 @@
           <t>His dark room , with its imitation oak wallpaper , smelled of fixative .</t>
         </is>
       </c>
+      <c r="O66" t="n">
+        <v/>
+      </c>
+      <c r="P66" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9819,6 +9886,12 @@
           <t>The summer of 1914 was drawing to a close , that terrible and threatening first summer of war , and the Moscow air already held the smell of wilting leaves and stagnant ponds , those sweet , cool aromas of autumn .</t>
         </is>
       </c>
+      <c r="O67" t="n">
+        <v/>
+      </c>
+      <c r="P67" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9846,6 +9919,12 @@
           <t>They smelled of bread .</t>
         </is>
       </c>
+      <c r="O68" t="n">
+        <v/>
+      </c>
+      <c r="P68" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9868,6 +9947,12 @@
           <t>What a smell !</t>
         </is>
       </c>
+      <c r="O69" t="n">
+        <v/>
+      </c>
+      <c r="P69" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9890,6 +9975,12 @@
           <t>My memory of the street is tied to the screech of trams as they crawled out of the depot ’s iron gates at dawn , the strap of my heavy conductor ’s satchel cutting into my shoulder and the sour smell of copper coins .</t>
         </is>
       </c>
+      <c r="O70" t="n">
+        <v/>
+      </c>
+      <c r="P70" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9912,6 +10003,12 @@
           <t>Draughty cars , floors covered with slippery mud and torn ticket stubs , the musty smell of wet clothing , smudgy windows , and outside , the never ending procession of small , dark wooden houses and rain lashed warehouse signs .</t>
         </is>
       </c>
+      <c r="O71" t="n">
+        <v/>
+      </c>
+      <c r="P71" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9939,6 +10036,12 @@
           <t>The air smelled of horse dung , mutton , hay and carpenters ’ glue .</t>
         </is>
       </c>
+      <c r="O72" t="n">
+        <v/>
+      </c>
+      <c r="P72" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9961,6 +10064,12 @@
           <t>I want him to smell the manure , if you ’ll excuse me , and hear the rooks .</t>
         </is>
       </c>
+      <c r="O73" t="n">
+        <v/>
+      </c>
+      <c r="P73" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9983,6 +10092,12 @@
           <t>Everything about him spoke of wealth and status : his slightly puffy eyes , the smell of fragrant cigar smoke , the white silk muffler of foreign make , the walking stick with a silver knob .</t>
         </is>
       </c>
+      <c r="O74" t="n">
+        <v/>
+      </c>
+      <c r="P74" t="n">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10010,6 +10125,12 @@
           <t>The buffet smelled of coffee and burnt onions .</t>
         </is>
       </c>
+      <c r="O75" t="n">
+        <v/>
+      </c>
+      <c r="P75" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10032,6 +10153,12 @@
           <t>The boy ’s eyes were filled with longing , for the things he did not have , like a simple hut with wide benches around its walls , a broken window covered over with paper , and the smell of warm rye bread with cinders baked into the crust .</t>
         </is>
       </c>
+      <c r="O76" t="n">
+        <v/>
+      </c>
+      <c r="P76" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10054,6 +10181,12 @@
           <t>Over the years I have often spent time in peasant huts and have come to love them for the dull sheen of their timber walls , the smell of ashes in the stove and their simple austerity , similar to that of fresh water from a spring , a bast basket or the unprepossessing flowers of a potato patch .</t>
         </is>
       </c>
+      <c r="O77" t="n">
+        <v/>
+      </c>
+      <c r="P77" t="n">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10081,6 +10214,12 @@
           <t>It smelled of dried raspberries .</t>
         </is>
       </c>
+      <c r="O78" t="n">
+        <v/>
+      </c>
+      <c r="P78" t="n">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10103,6 +10242,12 @@
           <t>Maybe it was because the danger had just passed , but the rain seemed warmer and the fields smelled of wet grass .</t>
         </is>
       </c>
+      <c r="O79" t="n">
+        <v/>
+      </c>
+      <c r="P79" t="n">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10125,6 +10270,12 @@
           <t>The air had the bitter almond smell of marsh flowers .</t>
         </is>
       </c>
+      <c r="O80" t="n">
+        <v/>
+      </c>
+      <c r="P80" t="n">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10152,6 +10303,12 @@
           <t>Everything smelled of blood , essence of valerian and burning alcohol .</t>
         </is>
       </c>
+      <c r="O81" t="n">
+        <v/>
+      </c>
+      <c r="P81" t="n">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10174,6 +10331,12 @@
           <t>Fleeting dreams of the smell of water and Marseilles soap filled my head .</t>
         </is>
       </c>
+      <c r="O82" t="n">
+        <v/>
+      </c>
+      <c r="P82" t="n">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10196,6 +10359,12 @@
           <t>But if you just walked a little way up the main street into town , you found yourself enveloped in silence and the smell of lilacs .</t>
         </is>
       </c>
+      <c r="O83" t="n">
+        <v/>
+      </c>
+      <c r="P83" t="n">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10218,6 +10387,12 @@
           <t>It was brightly lit inside and smelled of chocolate ; the two waitresses – sisters – were standing about chattering .</t>
         </is>
       </c>
+      <c r="O84" t="n">
+        <v/>
+      </c>
+      <c r="P84" t="n">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10240,6 +10415,12 @@
           <t>At a far table a sapper dozed , lulled to sleep by the warmth of the café , the smell of coffee and vanilla , and the muted voices of the blonde sisters .</t>
         </is>
       </c>
+      <c r="O85" t="n">
+        <v/>
+      </c>
+      <c r="P85" t="n">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10262,6 +10443,12 @@
           <t>The dust of defeat , with its bitter smell of charred ruins , covered everything – the soldiers ’ faces , the grain in the fields , the guns , the train .</t>
         </is>
       </c>
+      <c r="O86" t="n">
+        <v/>
+      </c>
+      <c r="P86" t="n">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10284,6 +10471,12 @@
           <t>But the train held onto the hot stuffy air of the day , especially in my operating carriage , whose windows were sealed up tight ; the smell of dressing and bandages had no escape .</t>
         </is>
       </c>
+      <c r="O87" t="n">
+        <v/>
+      </c>
+      <c r="P87" t="n">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10306,6 +10499,12 @@
           <t>There was the smell of sage .</t>
         </is>
       </c>
+      <c r="O88" t="n">
+        <v/>
+      </c>
+      <c r="P88" t="n">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10328,6 +10527,12 @@
           <t>It was then that this bitter smell became forever associated in my mind with the Black Sea .</t>
         </is>
       </c>
+      <c r="O89" t="n">
+        <v/>
+      </c>
+      <c r="P89" t="n">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10350,6 +10555,12 @@
           <t>I smelled mussels and fried mackerel – the nurses were cooking on an open fire near the house .</t>
         </is>
       </c>
+      <c r="O90" t="n">
+        <v/>
+      </c>
+      <c r="P90" t="n">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10372,6 +10583,12 @@
           <t>‘ In short , ’ the doctor said once we had reached his cabin , which smelled of a mixture of fresh salty sea air and fine tobacco , ‘ I need another orderly for the dressing station .</t>
         </is>
       </c>
+      <c r="O91" t="n">
+        <v/>
+      </c>
+      <c r="P91" t="n">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10394,6 +10611,12 @@
           <t>‘ It ’s all here in your head , it is , all those magical nights along the equator , the sunsets in Bengal , the smell of cinnamon and all that other nonsense .</t>
         </is>
       </c>
+      <c r="O92" t="n">
+        <v/>
+      </c>
+      <c r="P92" t="n">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10416,6 +10639,12 @@
           <t>There was the faint smell of violets on his moustache .</t>
         </is>
       </c>
+      <c r="O93" t="n">
+        <v/>
+      </c>
+      <c r="P93" t="n">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10438,6 +10667,12 @@
           <t>It was empty and reeked of stale smoke .</t>
         </is>
       </c>
+      <c r="O94" t="n">
+        <v/>
+      </c>
+      <c r="P94" t="n">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10460,6 +10695,12 @@
           <t>The sound of crying , indistinguishable from laughter ( and perhaps it really was laughter , the laughter of all those famished people , overjoyed by the smell of that hot beef ) , hung over the crowd .</t>
         </is>
       </c>
+      <c r="O95" t="n">
+        <v/>
+      </c>
+      <c r="P95" t="n">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10482,6 +10723,12 @@
           <t>Whose fault was it that death had chosen them – that it had come to their little village , where the periwinkles were still in blossom and where , perhaps , the smell of warm bread still lingered in the peasant huts , to drive them from their homes , hurrying and in tears , and to finish them off in a strange land , in thick sand , on a highway , where the metal rimmed wheels of carts creaked by just inches from their eternally resting faces ?</t>
         </is>
       </c>
+      <c r="O96" t="n">
+        <v/>
+      </c>
+      <c r="P96" t="n">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10504,6 +10751,12 @@
           <t>There was the faint smell of eau de Cologne .</t>
         </is>
       </c>
+      <c r="O97" t="n">
+        <v/>
+      </c>
+      <c r="P97" t="n">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10526,6 +10779,12 @@
           <t>Again the stench of horse sweat , the shouting , the creaking wheels , the hard saddle , and then the sand , ever more sand .</t>
         </is>
       </c>
+      <c r="O98" t="n">
+        <v/>
+      </c>
+      <c r="P98" t="n">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10548,6 +10807,12 @@
           <t>Dust from the horses and the wet smell of the bogs hung in the air .</t>
         </is>
       </c>
+      <c r="O99" t="n">
+        <v/>
+      </c>
+      <c r="P99" t="n">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10570,6 +10835,12 @@
           <t>We could not dry out and before long we began to smell like wet dogs in our greatcoats .</t>
         </is>
       </c>
+      <c r="O100" t="n">
+        <v/>
+      </c>
+      <c r="P100" t="n">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10592,6 +10863,12 @@
           <t>Not a wisp of smoke rose from the hovels , but for some reason the air smelled of scorched feathers .</t>
         </is>
       </c>
+      <c r="O101" t="n">
+        <v/>
+      </c>
+      <c r="P101" t="n">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10614,6 +10891,12 @@
           <t>A warm stench hit us in the face .</t>
         </is>
       </c>
+      <c r="O102" t="n">
+        <v/>
+      </c>
+      <c r="P102" t="n">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10636,6 +10919,12 @@
           <t>Their light blue uniforms smelled of eau de Cologne .</t>
         </is>
       </c>
+      <c r="O103" t="n">
+        <v/>
+      </c>
+      <c r="P103" t="n">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10658,6 +10947,12 @@
           <t>Sometimes the officers quarrelled , and you could almost smell gunpowder in the air of Uncle Kolya ’s small dining room and imagine the men reaching for their swords .</t>
         </is>
       </c>
+      <c r="O104" t="n">
+        <v/>
+      </c>
+      <c r="P104" t="n">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10680,6 +10975,12 @@
           <t>The room had the acidic smell of fixing solution .</t>
         </is>
       </c>
+      <c r="O105" t="n">
+        <v/>
+      </c>
+      <c r="P105" t="n">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10702,6 +11003,12 @@
           <t>It filled the rooms with its sound , its breeze , its scent .</t>
         </is>
       </c>
+      <c r="O106" t="n">
+        <v/>
+      </c>
+      <c r="P106" t="n">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10724,6 +11031,12 @@
           <t>The smell of seaweed drifted in through the open windows of the carriage .</t>
         </is>
       </c>
+      <c r="O107" t="n">
+        <v/>
+      </c>
+      <c r="P107" t="n">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10746,6 +11059,12 @@
           <t>The entire hotel reeked of cheap face powder , strong medicines and burnt fat from the kitchen .</t>
         </is>
       </c>
+      <c r="O108" t="n">
+        <v/>
+      </c>
+      <c r="P108" t="n">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10768,6 +11087,12 @@
           <t>As I read along , forgotten colours and smells and details of the place came back to me , but I could not place them .</t>
         </is>
       </c>
+      <c r="O109" t="n">
+        <v/>
+      </c>
+      <c r="P109" t="n">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10790,6 +11115,12 @@
           <t>If you bend over a gun , your heart beats faster – the water smells of the ocean and worm wood , it ’s a smell that clears your head and reminds you of long sea voyages , the kind that heal your soul and quicken the mind .</t>
         </is>
       </c>
+      <c r="O110" t="n">
+        <v/>
+      </c>
+      <c r="P110" t="n">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10812,6 +11143,12 @@
           <t>Or let the old sun bleached deck and the smell of the seaweed clinging to the boat ’s iron sides along the waterline suggest something else .</t>
         </is>
       </c>
+      <c r="O111" t="n">
+        <v/>
+      </c>
+      <c r="P111" t="n">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10834,6 +11171,12 @@
           <t>Her dark blue eyes never smiled , and her long black plaits smelled of lavender .</t>
         </is>
       </c>
+      <c r="O112" t="n">
+        <v/>
+      </c>
+      <c r="P112" t="n">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10856,6 +11199,12 @@
           <t>The sour smell of cabbage soup and samovar smoke wafted up from the restaurant .</t>
         </is>
       </c>
+      <c r="O113" t="n">
+        <v/>
+      </c>
+      <c r="P113" t="n">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10878,6 +11227,12 @@
           <t>The first February thaw had arrived , bringing with it a wet fog , blustery winds and the smell of smoke .</t>
         </is>
       </c>
+      <c r="O114" t="n">
+        <v/>
+      </c>
+      <c r="P114" t="n">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10900,6 +11255,12 @@
           <t>That smell , which brought to mind the fusty air of old fashioned apartments , gave him away .</t>
         </is>
       </c>
+      <c r="O115" t="n">
+        <v/>
+      </c>
+      <c r="P115" t="n">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10922,6 +11283,12 @@
           <t>For some reason I was convinced that medicinal smells like this were incompatible with the high calling of a champion of the people .</t>
         </is>
       </c>
+      <c r="O116" t="n">
+        <v/>
+      </c>
+      <c r="P116" t="n">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10944,6 +11311,12 @@
           <t>The air smelled of printers ’ ink and rye bread .</t>
         </is>
       </c>
+      <c r="O117" t="n">
+        <v/>
+      </c>
+      <c r="P117" t="n">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10966,6 +11339,12 @@
           <t>The army had brought the village smell of bread with them .</t>
         </is>
       </c>
+      <c r="O118" t="n">
+        <v/>
+      </c>
+      <c r="P118" t="n">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10988,6 +11367,12 @@
           <t>The wheels creaked , the old harness smelled of tar .</t>
         </is>
       </c>
+      <c r="O119" t="n">
+        <v/>
+      </c>
+      <c r="P119" t="n">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11010,6 +11395,12 @@
           <t>There was the slightly bitter smell of burned juniper berries , which the monks used instead of incense .</t>
         </is>
       </c>
+      <c r="O120" t="n">
+        <v/>
+      </c>
+      <c r="P120" t="n">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11032,6 +11423,12 @@
           <t>The late night air smelled of smoke from the burning houses .</t>
         </is>
       </c>
+      <c r="O121" t="n">
+        <v/>
+      </c>
+      <c r="P121" t="n">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11054,6 +11451,12 @@
           <t>The Moscow streets still smelled of printers ’ ink , and tattered scraps of old newspapers and posters clung to the walls .</t>
         </is>
       </c>
+      <c r="O122" t="n">
+        <v/>
+      </c>
+      <c r="P122" t="n">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11076,6 +11479,12 @@
           <t>They brought with them the aroma of apples , homespun and frost .</t>
         </is>
       </c>
+      <c r="O123" t="n">
+        <v/>
+      </c>
+      <c r="P123" t="n">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11098,6 +11507,12 @@
           <t>For some reason I found the apples ’ strong smell and the homespun ’s suggestion of warmth and durability comforting .</t>
         </is>
       </c>
+      <c r="O124" t="n">
+        <v/>
+      </c>
+      <c r="P124" t="n">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11120,6 +11535,12 @@
           <t>He even sniffed the envelopes , thinking he might pick up the sweet scent of tropical fruit , but they only smelled of leather and sealing wax .</t>
         </is>
       </c>
+      <c r="O125" t="n">
+        <v/>
+      </c>
+      <c r="P125" t="n">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11142,6 +11563,12 @@
           <t>He even sniffed the envelopes , thinking he might pick up the sweet scent of tropical fruit , but they only smelled of leather and sealing wax .</t>
         </is>
       </c>
+      <c r="O126" t="n">
+        <v/>
+      </c>
+      <c r="P126" t="n">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11164,6 +11591,12 @@
           <t>Immediately the stench of scorched wool filled the air .</t>
         </is>
       </c>
+      <c r="O127" t="n">
+        <v/>
+      </c>
+      <c r="P127" t="n">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -11186,6 +11619,12 @@
           <t>I caught the smell of rotting leaves , like the faint bouquet of wine , of bitter vegetable matter and last year ’s thawed out flowers , which seemed to be seeping out from deep down inside the damp , shelterless and long untended soil .</t>
         </is>
       </c>
+      <c r="O128" t="n">
+        <v/>
+      </c>
+      <c r="P128" t="n">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11208,6 +11647,12 @@
           <t>He never began the story with a description of the house , but with an elaborate discourse on the distinctive smell of Turkish wooden houses .</t>
         </is>
       </c>
+      <c r="O129" t="n">
+        <v/>
+      </c>
+      <c r="P129" t="n">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11230,6 +11675,12 @@
           <t>According to Rozovsky , they all smelled of the warm dust of rotting wood and of honey , particularly on hot , still afternoons when if you so much as touched the verandah railing it would singe your hand .</t>
         </is>
       </c>
+      <c r="O130" t="n">
+        <v/>
+      </c>
+      <c r="P130" t="n">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11252,6 +11703,12 @@
           <t>The smell of dust was always mixed with a faint hint of dry roses .</t>
         </is>
       </c>
+      <c r="O131" t="n">
+        <v/>
+      </c>
+      <c r="P131" t="n">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11274,6 +11731,12 @@
           <t>The smell of honey came from the surrounding olive gardens filled with wild roses .</t>
         </is>
       </c>
+      <c r="O132" t="n">
+        <v/>
+      </c>
+      <c r="P132" t="n">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11296,6 +11759,12 @@
           <t>Rozovsky first encountered the thick smell of dried roses and honey in Constantinople , when he was shown the gem encrusted casket holding the green banner of the Prophet .</t>
         </is>
       </c>
+      <c r="O133" t="n">
+        <v/>
+      </c>
+      <c r="P133" t="n">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11318,6 +11787,12 @@
           <t>There was a sour smell of wet greatcoats and carbolic acid .</t>
         </is>
       </c>
+      <c r="O134" t="n">
+        <v/>
+      </c>
+      <c r="P134" t="n">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11340,6 +11815,12 @@
           <t>I enjoyed the hall ’s dim light , its echoing emptiness , the two or three bulbs glowing in the crystal wall sconces deep in the corners and even that hotel smell of dusty carpets that no amount of airing could dispel .</t>
         </is>
       </c>
+      <c r="O135" t="n">
+        <v/>
+      </c>
+      <c r="P135" t="n">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11362,6 +11843,12 @@
           <t>Now and then the wind filled the street with the smell of stagnant water and tomato plants .</t>
         </is>
       </c>
+      <c r="O136" t="n">
+        <v/>
+      </c>
+      <c r="P136" t="n">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11384,6 +11871,12 @@
           <t>It all smelled like a chemist ’s shop .</t>
         </is>
       </c>
+      <c r="O137" t="n">
+        <v/>
+      </c>
+      <c r="P137" t="n">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11406,6 +11899,12 @@
           <t>Its green freshness was full of the rich smell of dill and mint .</t>
         </is>
       </c>
+      <c r="O138" t="n">
+        <v/>
+      </c>
+      <c r="P138" t="n">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11428,6 +11927,12 @@
           <t>Their strong smell seemed as though it had somehow been transported here from some springtime in a far off southern clime .</t>
         </is>
       </c>
+      <c r="O139" t="n">
+        <v/>
+      </c>
+      <c r="P139" t="n">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11450,6 +11955,12 @@
           <t>Everyone , I am sure , treasures in their soul some memory , as delicate as the scent of the lime trees in Noevsky Gardens , of a glimmer of happiness long buried under the squalor of everyday life .</t>
         </is>
       </c>
+      <c r="O140" t="n">
+        <v/>
+      </c>
+      <c r="P140" t="n">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11472,6 +11983,12 @@
           <t>Whenever our family passed the summer holidays near a railway station , I spent hours there meeting and seeing off every single train together with the station guard in his red cap . Even now , every last thing about railways still has for me the poetry of travel about it , all the way down to the smell of the coal smoke from the engine .</t>
         </is>
       </c>
+      <c r="O141" t="n">
+        <v/>
+      </c>
+      <c r="P141" t="n">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11494,6 +12011,12 @@
           <t>For some reason the smell of coffee coming from Frau Knoster ’s room brought back memories of Christmas Eve .</t>
         </is>
       </c>
+      <c r="O142" t="n">
+        <v/>
+      </c>
+      <c r="P142" t="n">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11516,6 +12039,12 @@
           <t>Pan Kturenda gave off a complex aroma of hair dye , stale tobacco and hooch , which he distilled himself in his own dimly lit room .</t>
         </is>
       </c>
+      <c r="O143" t="n">
+        <v/>
+      </c>
+      <c r="P143" t="n">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11538,6 +12067,12 @@
           <t>There was something comforting about the smell of old food that clung to the kitchens .</t>
         </is>
       </c>
+      <c r="O144" t="n">
+        <v/>
+      </c>
+      <c r="P144" t="n">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11560,6 +12095,12 @@
           <t>Everything was all jumbled together – Varya Panina&gt;1 and hand grenades , the smell of iodoform and the soft sing song of Ukrainian speech , the red cockades on the Cossack hats and symphony concerts , soldiers ’ dreams of still ponds amid peaceful meadows and the hysterical cries of illegal traders being rounded up in the bazaars .</t>
         </is>
       </c>
+      <c r="O145" t="n">
+        <v/>
+      </c>
+      <c r="P145" t="n">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11582,6 +12123,12 @@
           <t>They had brought with them the smell of battle , bullet ridden red banners , dashing songs and a selfless devotion to the revolution .</t>
         </is>
       </c>
+      <c r="O146" t="n">
+        <v/>
+      </c>
+      <c r="P146" t="n">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11604,6 +12151,12 @@
           <t>At long last , the lime trees blossomed in the parks , and their scent filtered into the houses sealed up tight over the winter and forced the city dwellers to throw open their windows and balcony doors .</t>
         </is>
       </c>
+      <c r="O147" t="n">
+        <v/>
+      </c>
+      <c r="P147" t="n">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11626,6 +12179,12 @@
           <t>The warm , drowsy smell of summer leaves drifted through the broken windows .</t>
         </is>
       </c>
+      <c r="O148" t="n">
+        <v/>
+      </c>
+      <c r="P148" t="n">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11648,6 +12207,12 @@
           <t>The barrack stench was so strong that it immediately settled into my clothes and never left .</t>
         </is>
       </c>
+      <c r="O149" t="n">
+        <v/>
+      </c>
+      <c r="P149" t="n">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11670,6 +12235,12 @@
           <t>There was the smell of dusty grass , and the bells of the Pechersk Monastery struck the useless hour of four o ’clock .</t>
         </is>
       </c>
+      <c r="O150" t="n">
+        <v/>
+      </c>
+      <c r="P150" t="n">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11692,6 +12263,12 @@
           <t>The air was filled with the smell of flowering stocks .</t>
         </is>
       </c>
+      <c r="O151" t="n">
+        <v/>
+      </c>
+      <c r="P151" t="n">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11714,6 +12291,12 @@
           <t>The smell of grass came from the front gardens .</t>
         </is>
       </c>
+      <c r="O152" t="n">
+        <v/>
+      </c>
+      <c r="P152" t="n">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11736,6 +12319,12 @@
           <t>Amalia ’s dark flat smelled of fresh coffee .</t>
         </is>
       </c>
+      <c r="O153" t="n">
+        <v/>
+      </c>
+      <c r="P153" t="n">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11758,6 +12347,12 @@
           <t>As always , the smell of coffee made the flat seem cosier , despite the ‘ Gift of the Sea ’ – a broken wall mounted thermometer decorated with cockle shells that read three degrees below zero both winter and summer .</t>
         </is>
       </c>
+      <c r="O154" t="n">
+        <v/>
+      </c>
+      <c r="P154" t="n">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11780,6 +12375,12 @@
           <t>Her flowers were pretty , but they smelled of paint and glue and very quickly gathered dust .</t>
         </is>
       </c>
+      <c r="O155" t="n">
+        <v/>
+      </c>
+      <c r="P155" t="n">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11802,6 +12403,12 @@
           <t>A great many women had travelled the same path from sin to sanctity , and as proof faint gold haloes had been lit over their heads in the paintings of the Great Masters of the Renaissance , and white lilies brushed their hems , spreading the scent of chastity .</t>
         </is>
       </c>
+      <c r="O156" t="n">
+        <v/>
+      </c>
+      <c r="P156" t="n">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11824,6 +12431,12 @@
           <t>The smell of marigolds drifted from behind the fences .</t>
         </is>
       </c>
+      <c r="O157" t="n">
+        <v/>
+      </c>
+      <c r="P157" t="n">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11846,6 +12459,12 @@
           <t>I would try to retrieve from my memory every last detail – the colour of the faded runners in the corridors , the wall paper designs , the various smells , the prints on the walls , the faces of the maids , the way they talked , the worn bentwood furniture – everything right down to the inkwells made of stone from the Urals the colour of damp sugar which were always filled with a few dead flies but never any ink .</t>
         </is>
       </c>
+      <c r="O158" t="n">
+        <v/>
+      </c>
+      <c r="P158" t="n">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11868,6 +12487,12 @@
           <t>The chestnuts crackled , burst and gave off an aroma of burnt bark , although sweeter and more fragrant .</t>
         </is>
       </c>
+      <c r="O159" t="n">
+        <v/>
+      </c>
+      <c r="P159" t="n">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11890,6 +12515,12 @@
           <t>I loved the smell of fog as well , which carried with it a scent of coal smoke and steam .</t>
         </is>
       </c>
+      <c r="O160" t="n">
+        <v/>
+      </c>
+      <c r="P160" t="n">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11912,6 +12543,12 @@
           <t>It was the smell of railway stations , of docks and ship decks – everything that spoke of travel , of long journeys over land and sea , of voyages through violet blue light to distant pink islands bathed in the sweet aroma of lemons , of the raw wind and warning lights in the English Channel , of the rhythmic clatter of a train rolling through our slumbering Russian forests , of everything that captivates our frail human hearts .</t>
         </is>
       </c>
+      <c r="O161" t="n">
+        <v/>
+      </c>
+      <c r="P161" t="n">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11934,6 +12571,12 @@
           <t>The cartridges had an acrid smell of gunpowder .</t>
         </is>
       </c>
+      <c r="O162" t="n">
+        <v/>
+      </c>
+      <c r="P162" t="n">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11955,6 +12598,12 @@
         <is>
           <t>I could tell by the smell of the wet shingle and the subtle trembling of the last leaf on the plane tree .</t>
         </is>
+      </c>
+      <c r="O163" t="n">
+        <v/>
+      </c>
+      <c r="P163" t="n">
+        <v/>
       </c>
     </row>
     <row r="164">
